--- a/GameConfig/Datas/通用/文本配置表.xlsx
+++ b/GameConfig/Datas/通用/文本配置表.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\GitHub Project\DGame_Fantasy\GameConfig\Datas\通用配置表\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\GitHub Project\DGame_Fantasy\GameConfig\Datas\通用\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D2EAD63-DB0C-4677-A611-E28F31FED241}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEC2CBEF-F426-401A-8D49-0092E39E5D42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="116">
   <si>
     <t>##var</t>
   </si>
@@ -430,6 +430,10 @@
   </si>
   <si>
     <t>角色名字含有非法字符</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>登录Token验证失败</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -583,7 +587,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -680,6 +684,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3624,7 +3631,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:AO49"/>
+  <dimension ref="A1:AO50"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="3" width="8.6640625" style="3"/>
@@ -4127,168 +4134,179 @@
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="27" t="s">
+      <c r="B22" s="3">
+        <v>1015</v>
+      </c>
+      <c r="D22" s="34" t="s">
+        <v>115</v>
+      </c>
+      <c r="E22" s="27" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="27" t="s">
         <v>90</v>
       </c>
-      <c r="E22" s="27"/>
-    </row>
-    <row r="23" spans="1:5" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="26" t="s">
+      <c r="E23" s="27"/>
+    </row>
+    <row r="24" spans="1:5" s="24" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="26" t="s">
         <v>90</v>
       </c>
-      <c r="D23" s="24" t="s">
+      <c r="D24" s="24" t="s">
         <v>105</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B24" s="3">
-        <v>2001</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="E24" s="27" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B25" s="3">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E25" s="27" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B26" s="3">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E26" s="27" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B27" s="3">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E27" s="27" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B28" s="3">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E28" s="27" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B29" s="3">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E29" s="27" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B30" s="3">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E30" s="27" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B31" s="3">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E31" s="27" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B32" s="3">
+        <v>2008</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="E32" s="27" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="33" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B33" s="3">
         <v>2009</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="D33" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="E32" s="27" t="s">
+      <c r="E33" s="27" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="33" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D33" s="15"/>
-    </row>
-    <row r="34" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:5" x14ac:dyDescent="0.3">
       <c r="D34" s="15"/>
     </row>
-    <row r="35" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:5" x14ac:dyDescent="0.3">
       <c r="D35" s="15"/>
     </row>
-    <row r="36" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:5" x14ac:dyDescent="0.3">
       <c r="D36" s="15"/>
     </row>
-    <row r="37" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:5" x14ac:dyDescent="0.3">
       <c r="D37" s="15"/>
     </row>
-    <row r="38" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:5" x14ac:dyDescent="0.3">
       <c r="D38" s="15"/>
     </row>
-    <row r="39" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:5" x14ac:dyDescent="0.3">
       <c r="D39" s="15"/>
     </row>
-    <row r="40" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:5" x14ac:dyDescent="0.3">
       <c r="D40" s="15"/>
     </row>
-    <row r="41" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:5" x14ac:dyDescent="0.3">
       <c r="D41" s="15"/>
     </row>
-    <row r="42" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:5" x14ac:dyDescent="0.3">
       <c r="D42" s="15"/>
     </row>
-    <row r="43" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:5" x14ac:dyDescent="0.3">
       <c r="D43" s="15"/>
     </row>
-    <row r="44" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:5" x14ac:dyDescent="0.3">
       <c r="D44" s="15"/>
     </row>
-    <row r="45" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:5" x14ac:dyDescent="0.3">
       <c r="D45" s="15"/>
     </row>
-    <row r="46" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:5" x14ac:dyDescent="0.3">
       <c r="D46" s="15"/>
     </row>
-    <row r="47" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:5" x14ac:dyDescent="0.3">
       <c r="D47" s="15"/>
     </row>
-    <row r="48" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:5" x14ac:dyDescent="0.3">
       <c r="D48" s="15"/>
     </row>
     <row r="49" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D49" s="15"/>
+    </row>
+    <row r="50" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D50" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="4">

--- a/GameConfig/Datas/通用/文本配置表.xlsx
+++ b/GameConfig/Datas/通用/文本配置表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\GitHub Project\DGame_Fantasy\GameConfig\Datas\通用\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\GitHub_Project\DGame_Fantasy\GameConfig\Datas\通用\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEC2CBEF-F426-401A-8D49-0092E39E5D42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{553FC63C-C8E6-44D4-82AA-1D7A84236DE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="通用文本" sheetId="1" r:id="rId1"/>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="135">
   <si>
     <t>##var</t>
   </si>
@@ -434,6 +434,82 @@
   </si>
   <si>
     <t>登录Token验证失败</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>系统开放</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>系统开放查询错误</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>组队</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>房间参数无效</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>房间不存在</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>玩家已在房间中</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>房间玩家数量配置无效</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>房间创建失败</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>主界面功能按钮</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>界面提示</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>章节配置表</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>农场危机</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>怪物如汹涌潮水般汹汹来袭，宁静的农场瞬间陷入危机四伏的境地。小心怪物！</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>无</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>怪物配置表</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>史莱姆</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>怪物名称</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>章节描述</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>章节名称</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -481,7 +557,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -515,6 +591,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -587,7 +669,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -671,6 +753,12 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -686,7 +774,17 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1074,7 +1172,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AO58"/>
+  <dimension ref="A1:AO63"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.25" style="3" customWidth="1"/>
@@ -1107,15 +1205,15 @@
       <c r="D1" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="28" t="s">
+      <c r="E1" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
-      <c r="J1" s="29"/>
-      <c r="K1" s="29"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="31"/>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
       <c r="N1" s="5"/>
@@ -1158,15 +1256,15 @@
         <v>6</v>
       </c>
       <c r="D2" s="18"/>
-      <c r="E2" s="30" t="s">
+      <c r="E2" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="31"/>
-      <c r="I2" s="31"/>
-      <c r="J2" s="31"/>
-      <c r="K2" s="31"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
+      <c r="J2" s="33"/>
+      <c r="K2" s="33"/>
       <c r="L2" s="10"/>
       <c r="M2" s="10"/>
       <c r="N2" s="10"/>
@@ -1205,13 +1303,13 @@
       <c r="B3" s="10"/>
       <c r="C3" s="10"/>
       <c r="D3" s="19"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="33"/>
-      <c r="G3" s="33"/>
-      <c r="H3" s="33"/>
-      <c r="I3" s="33"/>
-      <c r="J3" s="33"/>
-      <c r="K3" s="33"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="35"/>
+      <c r="G3" s="35"/>
+      <c r="H3" s="35"/>
+      <c r="I3" s="35"/>
+      <c r="J3" s="35"/>
+      <c r="K3" s="35"/>
       <c r="L3" s="10"/>
       <c r="M3" s="10"/>
       <c r="N3" s="10"/>
@@ -1254,15 +1352,15 @@
         <v>12</v>
       </c>
       <c r="D4" s="17"/>
-      <c r="E4" s="28" t="s">
+      <c r="E4" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="29"/>
-      <c r="G4" s="29"/>
-      <c r="H4" s="29"/>
-      <c r="I4" s="29"/>
-      <c r="J4" s="29"/>
-      <c r="K4" s="29"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="H4" s="31"/>
+      <c r="I4" s="31"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="31"/>
       <c r="L4" s="6"/>
       <c r="M4" s="5"/>
       <c r="N4" s="5"/>
@@ -1303,25 +1401,25 @@
       <c r="D5" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="8">
+      <c r="E5" s="28">
         <v>0</v>
       </c>
-      <c r="F5" s="8">
+      <c r="F5" s="28">
         <v>1</v>
       </c>
-      <c r="G5" s="8">
+      <c r="G5" s="28">
         <v>2</v>
       </c>
-      <c r="H5" s="8">
+      <c r="H5" s="28">
         <v>3</v>
       </c>
-      <c r="I5" s="8">
+      <c r="I5" s="28">
         <v>4</v>
       </c>
-      <c r="J5" s="8">
+      <c r="J5" s="28">
         <v>5</v>
       </c>
-      <c r="K5" s="8">
+      <c r="K5" s="28">
         <v>6</v>
       </c>
       <c r="L5" s="6"/>
@@ -1364,31 +1462,31 @@
       <c r="D6" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="8" t="str" cm="1">
+      <c r="E6" s="28" t="str" cm="1">
         <f t="array" ref="E6">INDEX([1]语言地区!$K:$K,MATCH(E5,[1]语言地区!$J:$J,0))</f>
         <v>中国</v>
       </c>
-      <c r="F6" s="8" t="str" cm="1">
+      <c r="F6" s="28" t="str" cm="1">
         <f t="array" ref="F6">INDEX([1]语言地区!$K:$K,MATCH(F5,[1]语言地区!$J:$J,0))</f>
         <v>欧美</v>
       </c>
-      <c r="G6" s="8" t="str" cm="1">
+      <c r="G6" s="28" t="str" cm="1">
         <f t="array" ref="G6">INDEX([1]语言地区!$K:$K,MATCH(G5,[1]语言地区!$J:$J,0))</f>
         <v>港澳台</v>
       </c>
-      <c r="H6" s="8" t="str" cm="1">
+      <c r="H6" s="28" t="str" cm="1">
         <f t="array" ref="H6">INDEX([1]语言地区!$K:$K,MATCH(H5,[1]语言地区!$J:$J,0))</f>
         <v>韩国</v>
       </c>
-      <c r="I6" s="8" t="str" cm="1">
+      <c r="I6" s="28" t="str" cm="1">
         <f t="array" ref="I6">INDEX([1]语言地区!$K:$K,MATCH(I5,[1]语言地区!$J:$J,0))</f>
         <v>日本</v>
       </c>
-      <c r="J6" s="8" t="str" cm="1">
+      <c r="J6" s="28" t="str" cm="1">
         <f t="array" ref="J6">INDEX([1]语言地区!$K:$K,MATCH(J5,[1]语言地区!$J:$J,0))</f>
         <v>越南</v>
       </c>
-      <c r="K6" s="8" t="str" cm="1">
+      <c r="K6" s="28" t="str" cm="1">
         <f t="array" ref="K6">INDEX([1]语言地区!$K:$K,MATCH(K5,[1]语言地区!$J:$J,0))</f>
         <v>印尼</v>
       </c>
@@ -1937,14 +2035,10 @@
       <c r="P34" s="14"/>
       <c r="S34" s="14"/>
     </row>
-    <row r="35" spans="1:19" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>9</v>
-      </c>
-      <c r="B35" t="s">
-        <v>55</v>
-      </c>
-      <c r="D35" s="16"/>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A35" s="27" t="s">
+        <v>90</v>
+      </c>
       <c r="E35" s="20"/>
       <c r="F35" s="14"/>
       <c r="G35" s="14"/>
@@ -1955,35 +2049,34 @@
       <c r="P35" s="14"/>
       <c r="S35" s="14"/>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="B36" s="3">
-        <v>10100001</v>
-      </c>
-      <c r="D36" s="21" t="s">
-        <v>55</v>
-      </c>
-      <c r="E36" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="14"/>
-      <c r="J36" s="14"/>
-      <c r="K36" s="14"/>
-      <c r="P36" s="14"/>
-      <c r="S36" s="14"/>
+    <row r="36" spans="1:19" s="39" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="36" t="s">
+        <v>90</v>
+      </c>
+      <c r="B36" s="36"/>
+      <c r="C36" s="37"/>
+      <c r="D36" s="36" t="s">
+        <v>124</v>
+      </c>
+      <c r="E36" s="38"/>
+      <c r="F36" s="38"/>
+      <c r="G36" s="38"/>
+      <c r="H36" s="38"/>
+      <c r="I36" s="38"/>
+      <c r="J36" s="38"/>
+      <c r="K36" s="38"/>
+      <c r="P36" s="38"/>
+      <c r="S36" s="38"/>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B37" s="3">
-        <v>10100002</v>
-      </c>
-      <c r="C37" s="14"/>
+        <v>10100001</v>
+      </c>
       <c r="D37" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="E37" s="3" t="s">
-        <v>57</v>
+      <c r="E37" s="20" t="s">
+        <v>56</v>
       </c>
       <c r="F37" s="14"/>
       <c r="G37" s="14"/>
@@ -1991,55 +2084,53 @@
       <c r="I37" s="14"/>
       <c r="J37" s="14"/>
       <c r="K37" s="14"/>
-      <c r="L37" s="14"/>
       <c r="P37" s="14"/>
       <c r="S37" s="14"/>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B38" s="3">
-        <v>10100003</v>
-      </c>
+        <v>10100002</v>
+      </c>
+      <c r="C38" s="14"/>
       <c r="D38" s="21" t="s">
         <v>55</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>58</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="F38" s="14"/>
+      <c r="G38" s="14"/>
+      <c r="H38" s="14"/>
+      <c r="I38" s="14"/>
+      <c r="J38" s="14"/>
+      <c r="K38" s="14"/>
+      <c r="L38" s="14"/>
       <c r="P38" s="14"/>
       <c r="S38" s="14"/>
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B39" s="3">
-        <v>10100004</v>
-      </c>
-      <c r="C39" s="14"/>
+        <v>10100003</v>
+      </c>
       <c r="D39" s="21" t="s">
         <v>55</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="14"/>
-      <c r="J39" s="14"/>
-      <c r="K39" s="14"/>
-      <c r="L39" s="14"/>
-      <c r="M39" s="14"/>
-      <c r="P39" s="22"/>
+        <v>58</v>
+      </c>
+      <c r="P39" s="14"/>
       <c r="S39" s="14"/>
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B40" s="3">
-        <v>10100005</v>
+        <v>10100004</v>
       </c>
       <c r="C40" s="14"/>
       <c r="D40" s="21" t="s">
         <v>55</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F40" s="14"/>
       <c r="G40" s="14"/>
@@ -2054,14 +2145,14 @@
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B41" s="3">
-        <v>10100006</v>
+        <v>10100005</v>
       </c>
       <c r="C41" s="14"/>
       <c r="D41" s="21" t="s">
         <v>55</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F41" s="14"/>
       <c r="G41" s="14"/>
@@ -2071,19 +2162,20 @@
       <c r="K41" s="14"/>
       <c r="L41" s="14"/>
       <c r="M41" s="14"/>
-      <c r="P41" s="14"/>
+      <c r="P41" s="22"/>
       <c r="S41" s="14"/>
     </row>
-    <row r="42" spans="1:19" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>9</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>62</v>
+    <row r="42" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B42" s="3">
+        <v>10100006</v>
       </c>
       <c r="C42" s="14"/>
-      <c r="D42" s="21"/>
-      <c r="E42" s="3"/>
+      <c r="D42" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>61</v>
+      </c>
       <c r="F42" s="14"/>
       <c r="G42" s="14"/>
       <c r="H42" s="14"/>
@@ -2096,16 +2188,11 @@
       <c r="S42" s="14"/>
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="B43" s="3">
-        <v>11000001</v>
+      <c r="A43" s="27" t="s">
+        <v>90</v>
       </c>
       <c r="C43" s="14"/>
-      <c r="D43" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>63</v>
-      </c>
+      <c r="D43" s="21"/>
       <c r="F43" s="14"/>
       <c r="G43" s="14"/>
       <c r="H43" s="14"/>
@@ -2117,101 +2204,242 @@
       <c r="P43" s="14"/>
       <c r="S43" s="14"/>
     </row>
-    <row r="44" spans="1:19" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B44" s="3">
+    <row r="44" spans="1:19" s="39" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="36" t="s">
+        <v>90</v>
+      </c>
+      <c r="B44" s="37"/>
+      <c r="C44" s="38"/>
+      <c r="D44" s="36" t="s">
+        <v>126</v>
+      </c>
+      <c r="E44" s="37"/>
+      <c r="F44" s="38"/>
+      <c r="G44" s="38"/>
+      <c r="H44" s="38"/>
+      <c r="I44" s="38"/>
+      <c r="J44" s="38"/>
+      <c r="K44" s="38"/>
+      <c r="L44" s="38"/>
+      <c r="M44" s="38"/>
+      <c r="P44" s="38"/>
+      <c r="S44" s="38"/>
+    </row>
+    <row r="45" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B45" s="3">
+        <v>10200001</v>
+      </c>
+      <c r="D45" s="40" t="s">
+        <v>134</v>
+      </c>
+      <c r="E45" s="27" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B46" s="3">
+        <v>10200002</v>
+      </c>
+      <c r="D46" s="40" t="s">
+        <v>133</v>
+      </c>
+      <c r="E46" s="27" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A47" s="27" t="s">
+        <v>90</v>
+      </c>
+      <c r="C47" s="14"/>
+      <c r="D47" s="21"/>
+      <c r="F47" s="14"/>
+      <c r="G47" s="14"/>
+      <c r="H47" s="14"/>
+      <c r="I47" s="14"/>
+      <c r="J47" s="14"/>
+      <c r="K47" s="14"/>
+      <c r="L47" s="14"/>
+      <c r="M47" s="14"/>
+      <c r="P47" s="14"/>
+      <c r="S47" s="14"/>
+    </row>
+    <row r="48" spans="1:19" s="39" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="36" t="s">
+        <v>90</v>
+      </c>
+      <c r="B48" s="37"/>
+      <c r="C48" s="38"/>
+      <c r="D48" s="36" t="s">
+        <v>130</v>
+      </c>
+      <c r="E48" s="37"/>
+      <c r="F48" s="38"/>
+      <c r="G48" s="38"/>
+      <c r="H48" s="38"/>
+      <c r="I48" s="38"/>
+      <c r="J48" s="38"/>
+      <c r="K48" s="38"/>
+      <c r="L48" s="38"/>
+      <c r="M48" s="38"/>
+      <c r="P48" s="38"/>
+      <c r="S48" s="38"/>
+    </row>
+    <row r="49" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B49" s="3">
+        <v>10300001</v>
+      </c>
+      <c r="D49" s="40" t="s">
+        <v>132</v>
+      </c>
+      <c r="E49" s="27" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="50" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A50" s="27" t="s">
+        <v>90</v>
+      </c>
+      <c r="C50" s="14"/>
+      <c r="D50" s="21"/>
+      <c r="F50" s="14"/>
+      <c r="G50" s="14"/>
+      <c r="H50" s="14"/>
+      <c r="I50" s="14"/>
+      <c r="J50" s="14"/>
+      <c r="K50" s="14"/>
+      <c r="L50" s="14"/>
+      <c r="M50" s="14"/>
+      <c r="P50" s="14"/>
+      <c r="S50" s="14"/>
+    </row>
+    <row r="51" spans="1:19" s="39" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="36" t="s">
+        <v>90</v>
+      </c>
+      <c r="B51" s="37"/>
+      <c r="C51" s="38"/>
+      <c r="D51" s="36" t="s">
+        <v>125</v>
+      </c>
+      <c r="E51" s="37"/>
+      <c r="F51" s="38"/>
+      <c r="G51" s="38"/>
+      <c r="H51" s="38"/>
+      <c r="I51" s="38"/>
+      <c r="J51" s="38"/>
+      <c r="K51" s="38"/>
+      <c r="L51" s="38"/>
+      <c r="M51" s="38"/>
+      <c r="P51" s="38"/>
+      <c r="S51" s="38"/>
+    </row>
+    <row r="52" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B52" s="3">
+        <v>11000001</v>
+      </c>
+      <c r="C52" s="14"/>
+      <c r="D52" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F52" s="14"/>
+      <c r="G52" s="14"/>
+      <c r="H52" s="14"/>
+      <c r="I52" s="14"/>
+      <c r="J52" s="14"/>
+      <c r="K52" s="14"/>
+      <c r="L52" s="14"/>
+      <c r="M52" s="14"/>
+      <c r="P52" s="14"/>
+      <c r="S52" s="14"/>
+    </row>
+    <row r="53" spans="1:19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="3"/>
+      <c r="B53" s="3">
         <v>11000002</v>
       </c>
-      <c r="C44" s="3"/>
-      <c r="D44" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="E44" s="3" t="s">
+      <c r="C53" s="3"/>
+      <c r="D53" s="40" t="s">
+        <v>125</v>
+      </c>
+      <c r="E53" s="3" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="B45"/>
-      <c r="C45"/>
-      <c r="D45" s="23"/>
-      <c r="E45"/>
-    </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="B46"/>
-      <c r="C46"/>
-      <c r="D46" s="23"/>
-      <c r="E46"/>
-    </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="B47"/>
-      <c r="C47"/>
-      <c r="D47" s="23"/>
-      <c r="E47"/>
-    </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="B48"/>
-      <c r="C48"/>
-      <c r="D48" s="23"/>
-      <c r="E48"/>
-    </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B49"/>
-      <c r="C49"/>
-      <c r="D49" s="23"/>
-      <c r="E49"/>
-    </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B50"/>
-      <c r="C50"/>
-      <c r="D50" s="23"/>
-      <c r="E50"/>
-    </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B51"/>
-      <c r="C51"/>
-      <c r="D51" s="23"/>
-      <c r="E51"/>
-    </row>
-    <row r="52" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B52"/>
-      <c r="C52"/>
-      <c r="D52" s="23"/>
-      <c r="E52"/>
-    </row>
-    <row r="53" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B53"/>
-      <c r="C53"/>
-      <c r="D53" s="23"/>
-      <c r="E53"/>
-    </row>
-    <row r="54" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B54"/>
+      <c r="F53" s="3"/>
+      <c r="G53" s="3"/>
+      <c r="H53" s="3"/>
+      <c r="I53" s="3"/>
+      <c r="J53" s="3"/>
+      <c r="K53" s="3"/>
+    </row>
+    <row r="54" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B54" s="3">
+        <v>11000003</v>
+      </c>
       <c r="C54"/>
-      <c r="D54" s="23"/>
-      <c r="E54"/>
-    </row>
-    <row r="55" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="D54" s="40" t="s">
+        <v>125</v>
+      </c>
+      <c r="E54" s="14" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="55" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B55"/>
       <c r="C55"/>
       <c r="D55" s="23"/>
       <c r="E55"/>
     </row>
-    <row r="56" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B56"/>
       <c r="C56"/>
       <c r="D56" s="23"/>
       <c r="E56"/>
     </row>
-    <row r="57" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B57"/>
       <c r="C57"/>
       <c r="D57" s="23"/>
       <c r="E57"/>
     </row>
-    <row r="58" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B58"/>
       <c r="C58"/>
       <c r="D58" s="23"/>
       <c r="E58"/>
+    </row>
+    <row r="59" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B59"/>
+      <c r="C59"/>
+      <c r="D59" s="23"/>
+      <c r="E59"/>
+    </row>
+    <row r="60" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B60"/>
+      <c r="C60"/>
+      <c r="D60" s="23"/>
+      <c r="E60"/>
+    </row>
+    <row r="61" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B61"/>
+      <c r="C61"/>
+      <c r="D61" s="23"/>
+      <c r="E61"/>
+    </row>
+    <row r="62" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B62"/>
+      <c r="C62"/>
+      <c r="D62" s="23"/>
+      <c r="E62"/>
+    </row>
+    <row r="63" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B63"/>
+      <c r="C63"/>
+      <c r="D63" s="23"/>
+      <c r="E63"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -2250,15 +2478,15 @@
       <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="28" t="s">
+      <c r="E1" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
-      <c r="J1" s="29"/>
-      <c r="K1" s="29"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="31"/>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
       <c r="N1" s="5"/>
@@ -2301,15 +2529,15 @@
         <v>6</v>
       </c>
       <c r="D2" s="12"/>
-      <c r="E2" s="30" t="s">
+      <c r="E2" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="31"/>
-      <c r="I2" s="31"/>
-      <c r="J2" s="31"/>
-      <c r="K2" s="31"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
+      <c r="J2" s="33"/>
+      <c r="K2" s="33"/>
       <c r="L2" s="10"/>
       <c r="M2" s="10"/>
       <c r="N2" s="10"/>
@@ -2348,13 +2576,13 @@
       <c r="B3" s="10"/>
       <c r="C3" s="10"/>
       <c r="D3" s="13"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="33"/>
-      <c r="G3" s="33"/>
-      <c r="H3" s="33"/>
-      <c r="I3" s="33"/>
-      <c r="J3" s="33"/>
-      <c r="K3" s="33"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="35"/>
+      <c r="G3" s="35"/>
+      <c r="H3" s="35"/>
+      <c r="I3" s="35"/>
+      <c r="J3" s="35"/>
+      <c r="K3" s="35"/>
       <c r="L3" s="10"/>
       <c r="M3" s="10"/>
       <c r="N3" s="10"/>
@@ -2397,15 +2625,15 @@
         <v>12</v>
       </c>
       <c r="D4" s="7"/>
-      <c r="E4" s="28" t="s">
+      <c r="E4" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="29"/>
-      <c r="G4" s="29"/>
-      <c r="H4" s="29"/>
-      <c r="I4" s="29"/>
-      <c r="J4" s="29"/>
-      <c r="K4" s="29"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="H4" s="31"/>
+      <c r="I4" s="31"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="31"/>
       <c r="L4" s="6"/>
       <c r="M4" s="5"/>
       <c r="N4" s="5"/>
@@ -2850,15 +3078,15 @@
       <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="28" t="s">
+      <c r="E1" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
-      <c r="J1" s="29"/>
-      <c r="K1" s="29"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="31"/>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
       <c r="N1" s="5"/>
@@ -2901,15 +3129,15 @@
         <v>6</v>
       </c>
       <c r="D2" s="12"/>
-      <c r="E2" s="30" t="s">
+      <c r="E2" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="31"/>
-      <c r="I2" s="31"/>
-      <c r="J2" s="31"/>
-      <c r="K2" s="31"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
+      <c r="J2" s="33"/>
+      <c r="K2" s="33"/>
       <c r="L2" s="10"/>
       <c r="M2" s="10"/>
       <c r="N2" s="10"/>
@@ -2948,13 +3176,13 @@
       <c r="B3" s="10"/>
       <c r="C3" s="10"/>
       <c r="D3" s="13"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="33"/>
-      <c r="G3" s="33"/>
-      <c r="H3" s="33"/>
-      <c r="I3" s="33"/>
-      <c r="J3" s="33"/>
-      <c r="K3" s="33"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="35"/>
+      <c r="G3" s="35"/>
+      <c r="H3" s="35"/>
+      <c r="I3" s="35"/>
+      <c r="J3" s="35"/>
+      <c r="K3" s="35"/>
       <c r="L3" s="10"/>
       <c r="M3" s="10"/>
       <c r="N3" s="10"/>
@@ -2997,15 +3225,15 @@
         <v>12</v>
       </c>
       <c r="D4" s="7"/>
-      <c r="E4" s="28" t="s">
+      <c r="E4" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="29"/>
-      <c r="G4" s="29"/>
-      <c r="H4" s="29"/>
-      <c r="I4" s="29"/>
-      <c r="J4" s="29"/>
-      <c r="K4" s="29"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="H4" s="31"/>
+      <c r="I4" s="31"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="31"/>
       <c r="L4" s="6"/>
       <c r="M4" s="5"/>
       <c r="N4" s="5"/>
@@ -3250,15 +3478,15 @@
       <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="28" t="s">
+      <c r="E1" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
-      <c r="J1" s="29"/>
-      <c r="K1" s="29"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="31"/>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
       <c r="N1" s="5"/>
@@ -3301,15 +3529,15 @@
         <v>6</v>
       </c>
       <c r="D2" s="12"/>
-      <c r="E2" s="30" t="s">
+      <c r="E2" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="31"/>
-      <c r="I2" s="31"/>
-      <c r="J2" s="31"/>
-      <c r="K2" s="31"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
+      <c r="J2" s="33"/>
+      <c r="K2" s="33"/>
       <c r="L2" s="10"/>
       <c r="M2" s="10"/>
       <c r="N2" s="10"/>
@@ -3348,13 +3576,13 @@
       <c r="B3" s="10"/>
       <c r="C3" s="10"/>
       <c r="D3" s="13"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="33"/>
-      <c r="G3" s="33"/>
-      <c r="H3" s="33"/>
-      <c r="I3" s="33"/>
-      <c r="J3" s="33"/>
-      <c r="K3" s="33"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="35"/>
+      <c r="G3" s="35"/>
+      <c r="H3" s="35"/>
+      <c r="I3" s="35"/>
+      <c r="J3" s="35"/>
+      <c r="K3" s="35"/>
       <c r="L3" s="10"/>
       <c r="M3" s="10"/>
       <c r="N3" s="10"/>
@@ -3397,15 +3625,15 @@
         <v>12</v>
       </c>
       <c r="D4" s="7"/>
-      <c r="E4" s="28" t="s">
+      <c r="E4" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="29"/>
-      <c r="G4" s="29"/>
-      <c r="H4" s="29"/>
-      <c r="I4" s="29"/>
-      <c r="J4" s="29"/>
-      <c r="K4" s="29"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="H4" s="31"/>
+      <c r="I4" s="31"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="31"/>
       <c r="L4" s="6"/>
       <c r="M4" s="5"/>
       <c r="N4" s="5"/>
@@ -3654,15 +3882,15 @@
       <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="28" t="s">
+      <c r="E1" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
-      <c r="J1" s="29"/>
-      <c r="K1" s="29"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="31"/>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
       <c r="N1" s="5"/>
@@ -3705,15 +3933,15 @@
         <v>6</v>
       </c>
       <c r="D2" s="12"/>
-      <c r="E2" s="30" t="s">
+      <c r="E2" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="31"/>
-      <c r="I2" s="31"/>
-      <c r="J2" s="31"/>
-      <c r="K2" s="31"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
+      <c r="J2" s="33"/>
+      <c r="K2" s="33"/>
       <c r="L2" s="10"/>
       <c r="M2" s="10"/>
       <c r="N2" s="10"/>
@@ -3752,13 +3980,13 @@
       <c r="B3" s="10"/>
       <c r="C3" s="10"/>
       <c r="D3" s="13"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="33"/>
-      <c r="G3" s="33"/>
-      <c r="H3" s="33"/>
-      <c r="I3" s="33"/>
-      <c r="J3" s="33"/>
-      <c r="K3" s="33"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="35"/>
+      <c r="G3" s="35"/>
+      <c r="H3" s="35"/>
+      <c r="I3" s="35"/>
+      <c r="J3" s="35"/>
+      <c r="K3" s="35"/>
       <c r="L3" s="10"/>
       <c r="M3" s="10"/>
       <c r="N3" s="10"/>
@@ -3801,15 +4029,15 @@
         <v>12</v>
       </c>
       <c r="D4" s="7"/>
-      <c r="E4" s="28" t="s">
+      <c r="E4" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="29"/>
-      <c r="G4" s="29"/>
-      <c r="H4" s="29"/>
-      <c r="I4" s="29"/>
-      <c r="J4" s="29"/>
-      <c r="K4" s="29"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="H4" s="31"/>
+      <c r="I4" s="31"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="31"/>
       <c r="L4" s="6"/>
       <c r="M4" s="5"/>
       <c r="N4" s="5"/>
@@ -4137,7 +4365,7 @@
       <c r="B22" s="3">
         <v>1015</v>
       </c>
-      <c r="D22" s="34" t="s">
+      <c r="D22" s="29" t="s">
         <v>115</v>
       </c>
       <c r="E22" s="27" t="s">
@@ -4246,7 +4474,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B33" s="3">
         <v>2009</v>
       </c>
@@ -4257,49 +4485,95 @@
         <v>114</v>
       </c>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" s="27" t="s">
+        <v>90</v>
+      </c>
       <c r="D34" s="15"/>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="D35" s="15"/>
-    </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="D36" s="15"/>
-    </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" s="37" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="36" t="s">
+        <v>90</v>
+      </c>
+      <c r="D35" s="36" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B36" s="3">
+        <v>3001</v>
+      </c>
+      <c r="D36" s="29" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37" s="27" t="s">
+        <v>90</v>
+      </c>
       <c r="D37" s="15"/>
     </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="D38" s="15"/>
-    </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="D39" s="15"/>
-    </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="D40" s="15"/>
-    </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="D41" s="15"/>
-    </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="D42" s="15"/>
-    </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="D43" s="15"/>
-    </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" s="37" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="36" t="s">
+        <v>90</v>
+      </c>
+      <c r="D38" s="36" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B39" s="3">
+        <v>4001</v>
+      </c>
+      <c r="D39" s="29" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B40" s="3">
+        <v>4002</v>
+      </c>
+      <c r="D40" s="29" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B41" s="3">
+        <v>4003</v>
+      </c>
+      <c r="D41" s="29" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B42" s="3">
+        <v>4004</v>
+      </c>
+      <c r="D42" s="29" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B43" s="3">
+        <v>4005</v>
+      </c>
+      <c r="D43" s="29" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D44" s="15"/>
     </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D45" s="15"/>
     </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D46" s="15"/>
     </row>
-    <row r="47" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D47" s="15"/>
     </row>
-    <row r="48" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D48" s="15"/>
     </row>
     <row r="49" spans="4:4" x14ac:dyDescent="0.3">
